--- a/docs/03_test/社員更新画面テスト.xlsx
+++ b/docs/03_test/社員更新画面テスト.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\fullness\cs-training\Web_App_Exercise\docs\03_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD64DEEF-A786-44BE-B2B3-F34DFBC1CA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA32716F-CBED-4476-948E-579A388D239D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AD2F379E-4E2E-4DC3-A67C-CB666878C08E}"/>
   </bookViews>
   <sheets>
-    <sheet name="社員登録テスト" sheetId="1" r:id="rId1"/>
+    <sheet name="社員更新テスト" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -576,34 +576,34 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1343,10 +1343,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="14"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="17" t="s">
@@ -1360,82 +1360,82 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="16"/>
+      <c r="B37" s="20"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20" t="s">
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
       <c r="J38" s="17" t="s">
         <v>9</v>
       </c>
@@ -1444,7 +1444,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="22"/>
+      <c r="A39" s="18"/>
       <c r="B39" s="6" t="s">
         <v>15</v>
       </c>
@@ -1469,8 +1469,8 @@
       <c r="I39" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5">
@@ -1526,7 +1526,7 @@
       <c r="F41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G41" s="14" t="s">
         <v>13</v>
       </c>
       <c r="H41" s="10" t="s">
@@ -1561,7 +1561,7 @@
       <c r="F42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G42" s="23" t="s">
+      <c r="G42" s="14" t="s">
         <v>13</v>
       </c>
       <c r="H42" s="11" t="s">
@@ -1596,7 +1596,7 @@
       <c r="F43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G43" s="23" t="s">
+      <c r="G43" s="14" t="s">
         <v>13</v>
       </c>
       <c r="H43" s="7" t="s">
@@ -1631,7 +1631,7 @@
       <c r="F44" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G44" s="23" t="s">
+      <c r="G44" s="14" t="s">
         <v>13</v>
       </c>
       <c r="H44" s="10" t="s">
@@ -1666,7 +1666,7 @@
       <c r="F45" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G45" s="23" t="s">
+      <c r="G45" s="14" t="s">
         <v>13</v>
       </c>
       <c r="H45" s="10" t="s">
@@ -1693,11 +1693,11 @@
       <c r="F49" s="8"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
@@ -1731,12 +1731,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="K38:K39"/>
-    <mergeCell ref="F38:I38"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A1:B1"/>
@@ -1746,6 +1740,12 @@
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="F38:I38"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
